--- a/diseases/d164/2010-2014.xlsx
+++ b/diseases/d164/2010-2014.xlsx
@@ -776,28 +776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -924,28 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1072,28 +1100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1220,28 +1262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1368,28 +1424,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1516,28 +1586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1664,28 +1748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1812,28 +1910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -1960,28 +2072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2108,28 +2234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2256,28 +2396,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2404,28 +2558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2552,28 +2720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -2700,28 +2882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -2848,28 +3044,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -2996,28 +3206,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3144,28 +3368,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3292,28 +3530,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -3440,28 +3692,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -3588,28 +3854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -3736,28 +4016,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -3884,28 +4178,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4032,28 +4340,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4180,28 +4502,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4328,28 +4664,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4476,28 +4826,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4624,28 +4988,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4772,28 +5150,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -4920,28 +5312,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5068,28 +5474,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5216,28 +5636,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5364,28 +5798,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -5512,28 +5960,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5660,28 +6122,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5808,28 +6284,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -5956,28 +6446,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6104,28 +6608,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6252,28 +6770,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6400,28 +6932,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6548,28 +7094,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6696,28 +7256,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -6844,28 +7418,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -6992,28 +7580,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7140,28 +7742,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7288,28 +7904,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7436,28 +8066,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7584,28 +8228,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -7732,28 +8390,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -7880,28 +8552,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8028,28 +8714,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8176,28 +8876,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8324,28 +9038,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8472,28 +9200,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -8620,28 +9362,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8768,28 +9524,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -8916,28 +9686,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9064,28 +9848,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9212,28 +10010,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9360,28 +10172,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9508,28 +10334,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9656,28 +10496,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -9804,28 +10658,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -9952,28 +10820,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -10100,28 +10982,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -10248,28 +11144,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10396,28 +11306,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10544,28 +11468,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -10692,28 +11630,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -10840,28 +11792,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -10988,28 +11954,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11136,28 +12116,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11284,28 +12278,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11432,28 +12440,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -11580,28 +12602,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -11728,28 +12764,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -11876,28 +12926,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12024,28 +13088,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -12172,28 +13250,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12320,28 +13412,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12468,28 +13574,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -12616,28 +13736,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -12764,28 +13898,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -12912,28 +14060,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -13060,28 +14222,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -13208,28 +14384,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -13356,28 +14546,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13504,28 +14708,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13652,28 +14870,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -13800,28 +15032,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -13948,28 +15194,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -14096,28 +15356,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14244,28 +15518,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14392,28 +15680,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14540,28 +15842,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -14688,28 +16004,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -14836,28 +16166,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -14984,28 +16328,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15132,28 +16490,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15280,28 +16652,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15428,28 +16814,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -15576,28 +16976,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -15724,28 +17138,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -15872,28 +17300,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16020,28 +17462,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -16168,28 +17624,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -16316,28 +17786,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16464,28 +17948,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -16612,28 +18110,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -16760,28 +18272,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -16908,28 +18434,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17056,28 +18596,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -17204,28 +18758,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -17352,28 +18920,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17500,28 +19082,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -17648,28 +19244,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -17796,28 +19406,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -17944,28 +19568,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -18092,28 +19730,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18240,28 +19892,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -18388,28 +20054,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">

--- a/diseases/d164/2010-2014.xlsx
+++ b/diseases/d164/2010-2014.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -783,7 +781,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -793,12 +791,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -808,11 +801,6 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -927,17 +915,15 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -945,7 +931,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -955,12 +941,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -970,11 +951,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1089,17 +1065,15 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -1107,7 +1081,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1117,12 +1091,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1132,11 +1101,6 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1251,17 +1215,15 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -1269,7 +1231,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1279,12 +1241,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1294,11 +1251,6 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1413,17 +1365,15 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -1431,7 +1381,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1441,12 +1391,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1456,11 +1401,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1575,17 +1515,15 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -1593,7 +1531,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1603,12 +1541,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1618,11 +1551,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1737,17 +1665,15 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -1755,7 +1681,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1765,12 +1691,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1780,11 +1701,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1899,17 +1815,15 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -1917,7 +1831,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1927,12 +1841,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1942,11 +1851,6 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2061,17 +1965,15 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -2079,7 +1981,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2089,12 +1991,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2104,11 +2001,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2223,17 +2115,15 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -2241,7 +2131,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2251,12 +2141,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2266,11 +2151,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2385,17 +2265,15 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -2403,7 +2281,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2413,12 +2291,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2428,11 +2301,6 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2547,17 +2415,15 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -2565,7 +2431,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2575,12 +2441,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2590,11 +2451,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2709,17 +2565,15 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -2727,7 +2581,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2737,12 +2591,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2752,11 +2601,6 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2871,17 +2715,15 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -2889,7 +2731,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2899,12 +2741,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2914,11 +2751,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3033,17 +2865,15 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -3051,7 +2881,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3061,12 +2891,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3076,11 +2901,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3195,17 +3015,15 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -3213,7 +3031,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3223,12 +3041,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3238,11 +3051,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3357,17 +3165,15 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -3375,7 +3181,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3385,12 +3191,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3400,11 +3201,6 @@
       </c>
       <c r="AT18" t="n">
         <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3519,17 +3315,15 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -3537,7 +3331,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3547,12 +3341,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3562,11 +3351,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3681,17 +3465,15 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -3699,7 +3481,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3709,12 +3491,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3724,11 +3501,6 @@
       </c>
       <c r="AT20" t="n">
         <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3843,17 +3615,15 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -3861,7 +3631,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3871,12 +3641,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3886,11 +3651,6 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4005,17 +3765,15 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4023,7 +3781,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4033,12 +3791,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4048,11 +3801,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4167,17 +3915,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4185,7 +3931,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4195,12 +3941,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4210,11 +3951,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4329,17 +4065,15 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4347,7 +4081,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4357,12 +4091,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4372,11 +4101,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4491,17 +4215,15 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4509,7 +4231,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4519,12 +4241,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4534,11 +4251,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4653,17 +4365,15 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4671,7 +4381,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4681,12 +4391,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4696,11 +4401,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4815,17 +4515,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4833,7 +4531,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4843,12 +4541,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4858,11 +4551,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4977,17 +4665,15 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -4995,7 +4681,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5005,12 +4691,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5020,11 +4701,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5139,17 +4815,15 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -5157,7 +4831,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -5167,12 +4841,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5182,11 +4851,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5301,17 +4965,15 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -5319,7 +4981,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5329,12 +4991,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5344,11 +5001,6 @@
       </c>
       <c r="AT30" t="n">
         <v>1</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5463,17 +5115,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -5481,7 +5131,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5491,12 +5141,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5506,11 +5151,6 @@
       </c>
       <c r="AT31" t="n">
         <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5625,17 +5265,15 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -5643,7 +5281,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5653,12 +5291,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5668,11 +5301,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5787,17 +5415,15 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -5805,7 +5431,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5815,12 +5441,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5830,11 +5451,6 @@
       </c>
       <c r="AT33" t="n">
         <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5949,17 +5565,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -5967,7 +5581,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5977,12 +5591,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5992,11 +5601,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6111,17 +5715,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -6129,7 +5731,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -6139,12 +5741,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6154,11 +5751,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6273,17 +5865,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -6291,7 +5881,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -6301,12 +5891,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -6316,11 +5901,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6435,17 +6015,15 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -6453,7 +6031,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6463,12 +6041,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6478,11 +6051,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6597,17 +6165,15 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -6615,7 +6181,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6625,12 +6191,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -6640,11 +6201,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6759,17 +6315,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -6777,7 +6331,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6787,12 +6341,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6802,11 +6351,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6921,17 +6465,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -6939,7 +6481,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6949,12 +6491,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6964,11 +6501,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7083,17 +6615,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -7101,7 +6631,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -7111,12 +6641,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7126,11 +6651,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7245,17 +6765,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -7263,7 +6781,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7273,12 +6791,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7288,11 +6801,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7407,17 +6915,15 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -7425,7 +6931,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7435,12 +6941,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7450,11 +6951,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7569,17 +7065,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -7587,7 +7081,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7597,12 +7091,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -7612,11 +7101,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7731,17 +7215,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -7749,7 +7231,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7759,12 +7241,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7774,11 +7251,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7893,17 +7365,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -7911,7 +7381,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7921,12 +7391,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7936,11 +7401,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8055,17 +7515,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -8073,7 +7531,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -8083,12 +7541,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -8098,11 +7551,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8217,17 +7665,15 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -8235,7 +7681,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8245,12 +7691,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -8260,11 +7701,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8379,17 +7815,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -8397,7 +7831,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8407,12 +7841,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -8422,11 +7851,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8541,17 +7965,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -8559,7 +7981,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8569,12 +7991,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -8584,11 +8001,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8703,17 +8115,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -8721,7 +8131,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8731,12 +8141,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8746,11 +8151,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8865,17 +8265,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -8883,7 +8281,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8893,12 +8291,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -8908,11 +8301,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -9027,17 +8415,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -9045,7 +8431,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9055,12 +8441,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -9070,11 +8451,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9189,17 +8565,15 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -9207,7 +8581,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9217,12 +8591,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -9232,11 +8601,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9351,17 +8715,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -9369,7 +8731,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9379,12 +8741,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -9394,11 +8751,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9513,17 +8865,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -9531,7 +8881,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9541,12 +8891,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -9556,11 +8901,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9675,17 +9015,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -9693,7 +9031,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9703,12 +9041,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -9718,11 +9051,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9837,17 +9165,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -9855,7 +9181,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9865,12 +9191,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -9880,11 +9201,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9999,17 +9315,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10017,7 +9331,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -10027,12 +9341,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -10042,11 +9351,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -10161,17 +9465,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10179,7 +9481,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -10189,12 +9491,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -10204,11 +9501,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10323,17 +9615,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10341,7 +9631,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10351,12 +9641,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -10366,11 +9651,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10485,17 +9765,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10503,7 +9781,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10513,12 +9791,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -10528,11 +9801,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10647,17 +9915,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10665,7 +9931,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10675,12 +9941,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -10690,11 +9951,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10809,17 +10065,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10827,7 +10081,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10837,12 +10091,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -10852,11 +10101,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10971,17 +10215,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -10989,7 +10231,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10999,12 +10241,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -11014,11 +10251,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11133,17 +10365,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -11151,7 +10381,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -11161,12 +10391,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -11176,11 +10401,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -11295,17 +10515,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -11313,7 +10531,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11323,12 +10541,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -11338,11 +10551,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11457,17 +10665,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -11475,7 +10681,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11485,12 +10691,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -11500,11 +10701,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11619,17 +10815,15 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -11637,7 +10831,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11647,12 +10841,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -11662,11 +10851,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11781,17 +10965,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -11799,7 +10981,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11809,12 +10991,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -11824,11 +11001,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11943,17 +11115,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -11961,7 +11131,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11971,12 +11141,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11986,11 +11151,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -12105,17 +11265,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -12123,7 +11281,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -12133,12 +11291,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -12148,11 +11301,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -12267,17 +11415,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -12285,7 +11431,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12295,12 +11441,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -12310,11 +11451,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -12429,17 +11565,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -12447,7 +11581,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12457,12 +11591,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -12472,11 +11601,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12591,17 +11715,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -12609,7 +11731,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12619,12 +11741,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -12634,11 +11751,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12753,17 +11865,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -12771,7 +11881,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12781,12 +11891,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -12796,11 +11901,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12915,17 +12015,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -12933,7 +12031,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12943,12 +12041,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -12958,11 +12051,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -13077,17 +12165,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -13095,7 +12181,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -13105,12 +12191,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -13120,11 +12201,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13239,17 +12315,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -13257,7 +12331,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13267,12 +12341,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -13282,11 +12351,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -13401,17 +12465,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -13419,7 +12481,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13429,12 +12491,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -13444,11 +12501,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -13563,17 +12615,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -13581,7 +12631,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13591,12 +12641,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -13606,11 +12651,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13725,17 +12765,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -13743,7 +12781,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13753,12 +12791,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -13768,11 +12801,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13887,17 +12915,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -13905,7 +12931,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13915,12 +12941,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -13930,11 +12951,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -14049,17 +13065,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -14067,7 +13081,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -14077,12 +13091,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -14092,11 +13101,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -14211,17 +13215,15 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -14229,7 +13231,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -14239,12 +13241,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -14254,11 +13251,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14373,17 +13365,15 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -14391,7 +13381,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14401,12 +13391,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -14416,11 +13401,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14535,17 +13515,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -14553,7 +13531,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14563,12 +13541,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -14578,11 +13551,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -14697,17 +13665,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -14715,7 +13681,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14725,12 +13691,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -14740,11 +13701,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14859,17 +13815,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -14877,7 +13831,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14887,12 +13841,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -14902,11 +13851,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -15021,17 +13965,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -15039,7 +13981,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -15049,12 +13991,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -15064,11 +14001,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -15183,17 +14115,15 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -15201,7 +14131,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -15211,12 +14141,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -15226,11 +14151,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15345,17 +14265,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -15363,7 +14281,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -15373,12 +14291,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -15388,11 +14301,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -15507,17 +14415,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -15525,7 +14431,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15535,12 +14441,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -15550,11 +14451,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -15669,17 +14565,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -15687,7 +14581,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15697,12 +14591,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -15712,11 +14601,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15831,17 +14715,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -15849,7 +14731,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15859,12 +14741,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -15874,11 +14751,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15993,17 +14865,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16011,7 +14881,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -16021,12 +14891,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -16036,11 +14901,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -16155,17 +15015,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16173,7 +15031,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -16183,12 +15041,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -16198,11 +15051,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -16317,17 +15165,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16335,7 +15181,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -16345,12 +15191,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -16360,11 +15201,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -16479,17 +15315,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16497,7 +15331,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -16507,12 +15341,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -16522,11 +15351,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -16641,17 +15465,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16659,7 +15481,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -16669,12 +15491,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -16684,11 +15501,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -16803,17 +15615,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16821,7 +15631,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16831,12 +15641,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -16846,11 +15651,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -16965,17 +15765,15 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -16983,7 +15781,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16993,12 +15791,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -17008,11 +15801,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -17127,17 +15915,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -17145,7 +15931,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -17155,12 +15941,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -17170,11 +15951,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -17289,17 +16065,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -17307,7 +16081,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -17317,12 +16091,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -17332,11 +16101,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -17451,17 +16215,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -17469,7 +16231,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -17479,12 +16241,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -17494,11 +16251,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -17613,17 +16365,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -17631,7 +16381,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17641,12 +16391,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -17656,11 +16401,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -17775,17 +16515,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -17793,7 +16531,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -17803,12 +16541,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -17818,11 +16551,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -17937,17 +16665,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -17955,7 +16681,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17965,12 +16691,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -17980,11 +16701,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -18099,17 +16815,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -18117,7 +16831,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -18127,12 +16841,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -18142,11 +16851,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -18261,17 +16965,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -18279,7 +16981,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -18289,12 +16991,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -18304,11 +17001,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -18423,17 +17115,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -18441,7 +17131,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -18451,12 +17141,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -18466,11 +17151,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -18585,17 +17265,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -18603,7 +17281,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -18613,12 +17291,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -18628,11 +17301,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -18747,17 +17415,15 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -18765,7 +17431,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -18775,12 +17441,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -18790,11 +17451,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18909,17 +17565,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -18927,7 +17581,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18937,12 +17591,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -18952,11 +17601,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -19071,17 +17715,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -19089,7 +17731,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -19099,12 +17741,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -19114,11 +17751,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -19233,17 +17865,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -19251,7 +17881,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -19261,12 +17891,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -19276,11 +17901,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -19395,17 +18015,15 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -19413,7 +18031,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -19423,12 +18041,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -19438,11 +18051,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -19557,17 +18165,15 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -19575,7 +18181,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -19585,12 +18191,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -19600,11 +18201,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -19719,17 +18315,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -19737,7 +18331,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -19747,12 +18341,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -19762,11 +18351,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -19881,17 +18465,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -19899,7 +18481,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -19909,12 +18491,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -19924,11 +18501,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -20043,17 +18615,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_9dc1d4c446b42c84df480fbc22a5</t>
@@ -20061,7 +18631,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -20071,12 +18641,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -20086,11 +18651,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
